--- a/output/pdf_financials_xlsx/TCS.xlsx
+++ b/output/pdf_financials_xlsx/TCS.xlsx
@@ -1720,7 +1720,7 @@
         <v>-0.741</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.346</v>
+        <v>-2.346</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>-0.741</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.346</v>
+        <v>-2.346</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>-0.9692736334026606</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>2.237375423203471</v>
+        <v>-2.237375423203471</v>
       </c>
       <c r="N32" s="1" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>-0.741</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>2.346</v>
+        <v>-2.346</v>
       </c>
       <c r="N99" s="1" t="inlineStr">
         <is>
@@ -56795,7 +56795,7 @@
         <v>-0.741</v>
       </c>
       <c r="P454" s="5" t="n">
-        <v>2.346</v>
+        <v>-2.346</v>
       </c>
       <c r="Q454" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TCS.xlsx
+++ b/output/pdf_financials_xlsx/TCS.xlsx
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.328</v>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.587</v>
+        <v>1.534</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.747</v>
+        <v>1.71</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1.357</v>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.291</v>
+        <v>2.238</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.227</v>
+        <v>2.19</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1.567</v>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5.585488943608747</v>
+        <v>5.456274227759222</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6.056238442293049</v>
+        <v>5.955618405308387</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>4.395018791720424</v>
@@ -92964,7 +92964,7 @@
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E802" s="5" t="n">
@@ -93070,7 +93070,7 @@
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E803" s="5" t="n">

--- a/output/pdf_financials_xlsx/TCS.xlsx
+++ b/output/pdf_financials_xlsx/TCS.xlsx
@@ -1150,16 +1150,16 @@
         <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.308</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.244</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.119</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.146</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         <v>-0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.128</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.324</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>-0</v>
@@ -2305,7 +2305,7 @@
         <v>-1.72</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>3.58</v>
+        <v>4.708</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2354,51 +2354,51 @@
         <v>0.21</v>
       </c>
       <c r="E28" s="3" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="N28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="O28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="P28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="Q28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>1.663</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>1.612</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>1.603</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>1.493</v>
-      </c>
       <c r="R28" s="3" t="n">
-        <v>1.304</v>
+        <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2.124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.725</v>
+        <v>-0.841</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>5.11</v>
+        <v>4.708</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-0.9483446480660309</v>
+        <v>-1.100079791756596</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>4.873396595298269</v>
+        <v>4.490010013828621</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -7087,28 +7087,28 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.704</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.621</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.789</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.907</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.743</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.794</v>
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
@@ -7116,10 +7116,10 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.879</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>0</v>
@@ -7843,16 +7843,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -7864,7 +7864,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="J112" s="1" t="inlineStr">
         <is>
@@ -46382,11 +46382,7 @@
           <t>Amortization of other intangible assets 9</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
+      <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -49926,11 +49922,7 @@
           <t>Amortization of other intangible assets 10</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -57052,11 +57044,7 @@
           <t>Amortization of other intangible assets 12</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
+      <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -59066,7 +59054,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -59270,11 +59262,7 @@
           <t>Amortization of other intangible assets 11</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -61714,7 +61702,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
           <t>-</t>
@@ -63594,7 +63586,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -69192,7 +69188,11 @@
           <t>Depreciation of property and equipment 11</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E572" t="inlineStr">
         <is>
           <t>-</t>
@@ -71408,7 +71408,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E593" t="inlineStr">
         <is>
           <t>-</t>
@@ -72564,7 +72568,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E604" s="5" t="n">
@@ -75498,7 +75502,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D632" t="inlineStr"/>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E632" s="5" t="n">
         <v>0.008</v>
       </c>
@@ -77602,7 +77610,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E652" t="inlineStr">
         <is>
           <t>-</t>
@@ -85462,7 +85474,11 @@
           <t>Net finance costs 18</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr"/>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E730" t="inlineStr">
         <is>
           <t>-</t>
@@ -88272,7 +88288,11 @@
           <t>Net finance costs 19</t>
         </is>
       </c>
-      <c r="D757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E757" t="inlineStr">
         <is>
           <t>-</t>
@@ -89104,7 +89124,11 @@
           <t>Net finance costs 20</t>
         </is>
       </c>
-      <c r="D765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E765" t="inlineStr">
         <is>
           <t>-</t>
@@ -92548,7 +92572,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E798" s="5" t="n">

--- a/output/pdf_financials_xlsx/TCS.xlsx
+++ b/output/pdf_financials_xlsx/TCS.xlsx
@@ -1018,7 +1018,7 @@
         <v>2.106</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1.544</v>
+        <v>1.417</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1.455</v>
@@ -1432,10 +1432,10 @@
         <v>-0.226</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-1.828</v>
+        <v>-0.313</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-4.403</v>
+        <v>0.401</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -4777,10 +4777,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K64" s="3" t="n">
+        <v>9.087</v>
       </c>
       <c r="L64" s="3" t="n">
         <v>0</v>
@@ -4972,13 +4970,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K67" s="3" t="n">
+        <v>2.626</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>4.325</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
@@ -5176,25 +5172,25 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.922</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.848</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.662</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.662</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="71">
@@ -5241,25 +5237,25 @@
         <v>1.022</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.231</v>
+        <v>2.153</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>1.216</v>
+        <v>2.064</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.2</v>
+        <v>1.862</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.2</v>
+        <v>1.862</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="72">
@@ -5507,19 +5503,19 @@
         <v>0.5</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.662</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.662</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.8120000000000001</v>
+        <v>0</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>0.531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5696,25 +5692,25 @@
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>9.157</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>8.295</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>5.181</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>5.181</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>1.302</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>0</v>
+        <v>4.759</v>
       </c>
     </row>
     <row r="79">
@@ -5761,25 +5757,25 @@
         <v>10.827</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>9.6</v>
+        <v>18.757</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>8.4</v>
+        <v>16.695</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>7.2</v>
+        <v>12.381</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>7.2</v>
+        <v>12.381</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>0</v>
+        <v>1.302</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>0</v>
+        <v>4.759</v>
       </c>
     </row>
     <row r="80">
@@ -5834,31 +5830,25 @@
         <v>0.2999898729049572</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.1772116690390877</v>
+        <v>0.3421194718499975</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.1433298554180951</v>
+        <v>0.2796094798032494</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.1223010060713714</v>
+        <v>0.2073730035088741</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.1223010060713714</v>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2073730035088741</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.03092044640114672</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0.01849513064466336</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>0.08494444087609994</v>
       </c>
     </row>
     <row r="81">
@@ -6165,25 +6155,25 @@
         <v>2.333</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>9.157</v>
+        <v>0</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>8.295</v>
+        <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>5.181</v>
+        <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>5.181</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>1.798</v>
+        <v>0.496</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>0.761</v>
+        <v>0.033</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>4.759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -8076,7 +8066,7 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -8095,28 +8085,28 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.161</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.173</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.063</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.189</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.348</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.134</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.374</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.125</v>
       </c>
       <c r="J116" s="1" t="inlineStr">
         <is>
@@ -8124,22 +8114,22 @@
         </is>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.281</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.16</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.196</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.569</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.255</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.062</v>
       </c>
       <c r="Q116" s="3" t="n">
         <v>0</v>
@@ -8148,7 +8138,7 @@
         <v>0</v>
       </c>
       <c r="S116" s="3" t="n">
-        <v>0</v>
+        <v>-1.975</v>
       </c>
     </row>
     <row r="117">
@@ -11846,7 +11836,11 @@
           <t>Lease obligations 10</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12256,7 +12250,11 @@
           <t>Lease obligations 10</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -14808,7 +14806,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -15124,7 +15126,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -17942,7 +17948,11 @@
           <t>Lease obligations 12 812</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -18378,7 +18388,11 @@
           <t>Lease obligations 12 1,302</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -22266,7 +22280,11 @@
           <t>Lease obligations 12 793</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -22814,7 +22832,11 @@
           <t>Lease obligations 12 2,120</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -24824,7 +24846,11 @@
           <t>Lease obligations 12</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -25140,7 +25166,11 @@
           <t>Lease obligations 12</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -29278,7 +29308,11 @@
           <t>Lease obligations 14</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -29710,7 +29744,11 @@
           <t>Lease obligations 14</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -49004,7 +49042,11 @@
           <t>Acquisition of intangible assets 4</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -53206,7 +53248,11 @@
           <t>Proceeds from short-term investments 4</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -53924,7 +53970,11 @@
           <t>Acquisitions of other intangible assets 10</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -58534,7 +58584,11 @@
           <t>Acquisitions of other intangible assets 12</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -60754,7 +60808,11 @@
           <t>Acquisitions of other intangible assets 11</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -63696,7 +63754,11 @@
           <t>Acquisitions of other intangible assets 10</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -66124,7 +66186,11 @@
           <t>Acquisitions of other intangible assets 11</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E543" t="inlineStr">
         <is>
           <t>-</t>
@@ -68344,7 +68410,11 @@
           <t>Acquisitions of other intangible assets 10</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -71516,7 +71586,11 @@
           <t>Acquisitions of other intangible assets 12</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E594" t="inlineStr">
         <is>
           <t>-</t>
@@ -75608,7 +75682,11 @@
           <t>Acquisitions of intangible assets</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E633" s="5" t="n">
         <v>-0.161</v>
       </c>
@@ -88396,7 +88474,11 @@
           <t>Income tax (recovery) expense 15</t>
         </is>
       </c>
-      <c r="D758" t="inlineStr"/>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E758" t="inlineStr">
         <is>
           <t>-</t>
@@ -92884,7 +92966,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D801" t="inlineStr"/>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E801" s="5" t="n">
         <v>2.181</v>
       </c>
@@ -94562,7 +94648,11 @@
           <t>Income taxes recovery (note 12)</t>
         </is>
       </c>
-      <c r="D817" t="inlineStr"/>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E817" t="inlineStr">
         <is>
           <t>-</t>
